--- a/inp_Excel/ana_viaggi.xlsx
+++ b/inp_Excel/ana_viaggi.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="210">
   <si>
     <t>VIAGGIO_ID</t>
   </si>
@@ -387,6 +387,15 @@
   </si>
   <si>
     <t>3 GIORNI DI PURO ENDURO</t>
+  </si>
+  <si>
+    <t>PORTOGALLO IN 4X4</t>
+  </si>
+  <si>
+    <t>Un viaggio nel cuore di questa nazione</t>
+  </si>
+  <si>
+    <t>https://www.sardegnafuoritraccia.it/it/tour/fuoristrada-estero/nord-portugal-4x4</t>
   </si>
   <si>
     <t>4X4 - BALCANI ADVENTURE</t>
@@ -760,8 +769,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:W63" totalsRowShown="0" headerRowCount="1">
-  <autoFilter ref="A1:W63"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:W64" totalsRowShown="0" headerRowCount="1">
+  <autoFilter ref="A1:W64"/>
   <tableColumns count="23">
     <tableColumn id="1" name="VIAGGIO_ID"/>
     <tableColumn id="2" name="VIAGGIO_DESCRIZIONE_BREVE"/>
@@ -2817,7 +2826,7 @@
     </row>
     <row r="35" customHeight="1" ht="20">
       <c r="A35" s="5" t="n">
-        <v>23</v>
+        <v>861</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>121</v>
@@ -2826,19 +2835,19 @@
         <v>122</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="5" t="n">
@@ -2848,16 +2857,16 @@
         <v>14</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>44420.4166319444</v>
+        <v>46031.304849537</v>
       </c>
       <c r="P35" s="6"/>
       <c r="Q35" s="7"/>
@@ -2867,36 +2876,32 @@
       <c r="S35" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="T35" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="U35" s="6" t="s">
-        <v>124</v>
-      </c>
+      <c r="T35" s="6"/>
+      <c r="U35" s="6"/>
       <c r="V35" s="6"/>
       <c r="W35" s="6"/>
     </row>
     <row r="36" customHeight="1" ht="20">
       <c r="A36" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="D36" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>304</v>
+        <v>1700</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>56</v>
@@ -2909,21 +2914,21 @@
         <v>14</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O36" s="7" t="n">
-        <v>44420.4193634259</v>
+        <v>44420.4166319444</v>
       </c>
       <c r="P36" s="6"/>
       <c r="Q36" s="7"/>
       <c r="R36" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S36" s="6" t="s">
         <v>28</v>
@@ -2932,32 +2937,32 @@
         <v>29</v>
       </c>
       <c r="U36" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="V36" s="6"/>
       <c r="W36" s="6"/>
     </row>
-    <row r="37" customHeight="1" ht="29">
+    <row r="37" customHeight="1" ht="20">
       <c r="A37" s="5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B37" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="D37" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1000</v>
+        <v>304</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>56</v>
@@ -2967,10 +2972,10 @@
         <v>1</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="M37" s="5" t="n">
         <v>10</v>
@@ -2979,12 +2984,12 @@
         <v>26</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>44420.5078125</v>
+        <v>44420.4193634259</v>
       </c>
       <c r="P37" s="6"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S37" s="6" t="s">
         <v>28</v>
@@ -2993,45 +2998,45 @@
         <v>29</v>
       </c>
       <c r="U37" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="V37" s="6"/>
       <c r="W37" s="6"/>
     </row>
-    <row r="38" customHeight="1" ht="20">
+    <row r="38" customHeight="1" ht="29">
       <c r="A38" s="5" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>133</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I38" s="6"/>
       <c r="J38" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="M38" s="5" t="n">
         <v>10</v>
@@ -3040,47 +3045,53 @@
         <v>26</v>
       </c>
       <c r="O38" s="7" t="n">
-        <v>44468.751412037</v>
+        <v>44420.5078125</v>
       </c>
       <c r="P38" s="6"/>
       <c r="Q38" s="7"/>
-      <c r="R38" s="6"/>
+      <c r="R38" s="6" t="s">
+        <v>134</v>
+      </c>
       <c r="S38" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="T38" s="6"/>
-      <c r="U38" s="6"/>
+      <c r="T38" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="U38" s="6" t="s">
+        <v>135</v>
+      </c>
       <c r="V38" s="6"/>
       <c r="W38" s="6"/>
     </row>
-    <row r="39" customHeight="1" ht="43,5">
+    <row r="39" customHeight="1" ht="20">
       <c r="A39" s="5" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E39" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F39" s="6" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>205</v>
+        <v>350</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I39" s="6"/>
       <c r="J39" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K39" s="5" t="n">
         <v>13</v>
@@ -3095,34 +3106,28 @@
         <v>26</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>44594.3402662037</v>
+        <v>44468.751412037</v>
       </c>
       <c r="P39" s="6"/>
       <c r="Q39" s="7"/>
-      <c r="R39" s="6" t="s">
-        <v>136</v>
-      </c>
+      <c r="R39" s="6"/>
       <c r="S39" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="T39" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="U39" s="6" t="s">
-        <v>138</v>
-      </c>
+      <c r="T39" s="6"/>
+      <c r="U39" s="6"/>
       <c r="V39" s="6"/>
       <c r="W39" s="6"/>
     </row>
-    <row r="40" customHeight="1" ht="29">
+    <row r="40" customHeight="1" ht="43,5">
       <c r="A40" s="5" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>2</v>
@@ -3134,7 +3139,7 @@
         <v>24</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>25</v>
@@ -3156,34 +3161,34 @@
         <v>26</v>
       </c>
       <c r="O40" s="7" t="n">
-        <v>44615.8342361111</v>
+        <v>44594.3402662037</v>
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="7"/>
       <c r="R40" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="S40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="T40" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="U40" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="S40" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="T40" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="U40" s="6" t="s">
-        <v>142</v>
       </c>
       <c r="V40" s="6"/>
       <c r="W40" s="6"/>
     </row>
-    <row r="41" customHeight="1" ht="87">
+    <row r="41" customHeight="1" ht="29">
       <c r="A41" s="5" t="n">
-        <v>181</v>
+        <v>101</v>
       </c>
       <c r="B41" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="D41" s="5" t="n">
         <v>2</v>
@@ -3195,7 +3200,7 @@
         <v>24</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>25</v>
@@ -3217,34 +3222,34 @@
         <v>26</v>
       </c>
       <c r="O41" s="7" t="n">
-        <v>44810.5888425926</v>
+        <v>44615.8342361111</v>
       </c>
       <c r="P41" s="6"/>
       <c r="Q41" s="7"/>
       <c r="R41" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="S41" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="T41" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="U41" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="S41" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="T41" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="U41" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="V41" s="6"/>
       <c r="W41" s="6"/>
     </row>
-    <row r="42" customHeight="1" ht="43,5">
+    <row r="42" customHeight="1" ht="87">
       <c r="A42" s="5" t="n">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="B42" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>2</v>
@@ -3256,7 +3261,7 @@
         <v>24</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>25</v>
@@ -3278,56 +3283,56 @@
         <v>26</v>
       </c>
       <c r="O42" s="7" t="n">
-        <v>44834.2956712963</v>
+        <v>44810.5888425926</v>
       </c>
       <c r="P42" s="6"/>
       <c r="Q42" s="7"/>
       <c r="R42" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="S42" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="T42" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="U42" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="S42" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="T42" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="U42" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="V42" s="6"/>
       <c r="W42" s="6"/>
     </row>
     <row r="43" customHeight="1" ht="43,5">
       <c r="A43" s="5" t="n">
-        <v>741</v>
+        <v>201</v>
       </c>
       <c r="B43" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>152</v>
-      </c>
       <c r="D43" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>650</v>
+        <v>240</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I43" s="6"/>
       <c r="J43" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L43" s="5" t="n">
         <v>110</v>
@@ -3336,27 +3341,31 @@
         <v>10</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="O43" s="7" t="n">
-        <v>45951.6437962963</v>
+        <v>44834.2956712963</v>
       </c>
       <c r="P43" s="6"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="S43" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="T43" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="U43" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="S43" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
     </row>
-    <row r="44" customHeight="1" ht="20">
+    <row r="44" customHeight="1" ht="43,5">
       <c r="A44" s="5" t="n">
-        <v>622</v>
+        <v>741</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>154</v>
@@ -3365,10 +3374,10 @@
         <v>155</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>24</v>
@@ -3396,7 +3405,7 @@
         <v>60</v>
       </c>
       <c r="O44" s="7" t="n">
-        <v>45700.7497453704</v>
+        <v>45951.6437962963</v>
       </c>
       <c r="P44" s="6"/>
       <c r="Q44" s="7"/>
@@ -3413,7 +3422,7 @@
     </row>
     <row r="45" customHeight="1" ht="20">
       <c r="A45" s="5" t="n">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>157</v>
@@ -3422,16 +3431,16 @@
         <v>158</v>
       </c>
       <c r="D45" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E45" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="F45" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>56</v>
@@ -3441,19 +3450,19 @@
         <v>1</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L45" s="5" t="n">
         <v>110</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>60</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>45700.7520138889</v>
+        <v>45700.7497453704</v>
       </c>
       <c r="P45" s="6"/>
       <c r="Q45" s="7"/>
@@ -3470,7 +3479,7 @@
     </row>
     <row r="46" customHeight="1" ht="20">
       <c r="A46" s="5" t="n">
-        <v>761</v>
+        <v>624</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>160</v>
@@ -3479,16 +3488,16 @@
         <v>161</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>56</v>
@@ -3498,23 +3507,25 @@
         <v>1</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>110</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>60</v>
       </c>
       <c r="O46" s="7" t="n">
-        <v>45963.3376273148</v>
+        <v>45700.7520138889</v>
       </c>
       <c r="P46" s="6"/>
       <c r="Q46" s="7"/>
-      <c r="R46" s="6"/>
+      <c r="R46" s="6" t="s">
+        <v>162</v>
+      </c>
       <c r="S46" s="6" t="s">
         <v>28</v>
       </c>
@@ -3525,13 +3536,13 @@
     </row>
     <row r="47" customHeight="1" ht="20">
       <c r="A47" s="5" t="n">
-        <v>781</v>
+        <v>761</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>6</v>
@@ -3543,7 +3554,7 @@
         <v>24</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>56</v>
@@ -3565,7 +3576,7 @@
         <v>60</v>
       </c>
       <c r="O47" s="7" t="n">
-        <v>45964.9283101852</v>
+        <v>45963.3376273148</v>
       </c>
       <c r="P47" s="6"/>
       <c r="Q47" s="7"/>
@@ -3578,27 +3589,27 @@
       <c r="V47" s="6"/>
       <c r="W47" s="6"/>
     </row>
-    <row r="48" customHeight="1" ht="29">
+    <row r="48" customHeight="1" ht="20">
       <c r="A48" s="5" t="n">
-        <v>42</v>
+        <v>781</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>2300</v>
+        <v>880</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>56</v>
@@ -3608,25 +3619,23 @@
         <v>1</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="M48" s="5" t="n">
         <v>10</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="O48" s="7" t="n">
-        <v>44445.445150463</v>
+        <v>45964.9283101852</v>
       </c>
       <c r="P48" s="6"/>
       <c r="Q48" s="7"/>
-      <c r="R48" s="6" t="s">
-        <v>166</v>
-      </c>
+      <c r="R48" s="6"/>
       <c r="S48" s="6" t="s">
         <v>28</v>
       </c>
@@ -3635,9 +3644,9 @@
       <c r="V48" s="6"/>
       <c r="W48" s="6"/>
     </row>
-    <row r="49" customHeight="1" ht="43,5">
+    <row r="49" customHeight="1" ht="29">
       <c r="A49" s="5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>167</v>
@@ -3646,19 +3655,19 @@
         <v>168</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>600</v>
+        <v>2300</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I49" s="6"/>
       <c r="J49" s="5" t="n">
@@ -3668,7 +3677,7 @@
         <v>13</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="M49" s="5" t="n">
         <v>10</v>
@@ -3677,7 +3686,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="7" t="n">
-        <v>44445.4470717593</v>
+        <v>44445.445150463</v>
       </c>
       <c r="P49" s="6"/>
       <c r="Q49" s="7"/>
@@ -3692,9 +3701,9 @@
       <c r="V49" s="6"/>
       <c r="W49" s="6"/>
     </row>
-    <row r="50" customHeight="1" ht="29">
+    <row r="50" customHeight="1" ht="43,5">
       <c r="A50" s="5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>170</v>
@@ -3734,14 +3743,10 @@
         <v>26</v>
       </c>
       <c r="O50" s="7" t="n">
-        <v>44445</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q50" s="7" t="n">
-        <v>45479.6319907407</v>
-      </c>
+        <v>44445.4470717593</v>
+      </c>
+      <c r="P50" s="6"/>
+      <c r="Q50" s="7"/>
       <c r="R50" s="6" t="s">
         <v>172</v>
       </c>
@@ -3753,9 +3758,9 @@
       <c r="V50" s="6"/>
       <c r="W50" s="6"/>
     </row>
-    <row r="51" customHeight="1" ht="72,5">
+    <row r="51" customHeight="1" ht="29">
       <c r="A51" s="5" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>173</v>
@@ -3764,16 +3769,16 @@
         <v>174</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>280</v>
+        <v>600</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>25</v>
@@ -3795,10 +3800,14 @@
         <v>26</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>44445.4529976852</v>
-      </c>
-      <c r="P51" s="6"/>
-      <c r="Q51" s="7"/>
+        <v>44445</v>
+      </c>
+      <c r="P51" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q51" s="7" t="n">
+        <v>45479.6319907407</v>
+      </c>
       <c r="R51" s="6" t="s">
         <v>175</v>
       </c>
@@ -3810,9 +3819,9 @@
       <c r="V51" s="6"/>
       <c r="W51" s="6"/>
     </row>
-    <row r="52" customHeight="1" ht="43,5">
+    <row r="52" customHeight="1" ht="72,5">
       <c r="A52" s="5" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>176</v>
@@ -3821,16 +3830,16 @@
         <v>177</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>25</v>
@@ -3840,19 +3849,19 @@
         <v>1</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L52" s="5" t="n">
         <v>110</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O52" s="7" t="n">
-        <v>44445.4599768519</v>
+        <v>44445.4529976852</v>
       </c>
       <c r="P52" s="6"/>
       <c r="Q52" s="7"/>
@@ -3862,36 +3871,32 @@
       <c r="S52" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="T52" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="U52" s="6" t="s">
-        <v>179</v>
-      </c>
+      <c r="T52" s="6"/>
+      <c r="U52" s="6"/>
       <c r="V52" s="6"/>
       <c r="W52" s="6"/>
     </row>
-    <row r="53" customHeight="1" ht="101,5">
+    <row r="53" customHeight="1" ht="43,5">
       <c r="A53" s="5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B53" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C53" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>181</v>
-      </c>
       <c r="D53" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>25</v>
@@ -3901,36 +3906,40 @@
         <v>1</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L53" s="5" t="n">
         <v>110</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N53" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O53" s="7" t="n">
-        <v>44445.4633449074</v>
+        <v>44445.4599768519</v>
       </c>
       <c r="P53" s="6"/>
       <c r="Q53" s="7"/>
       <c r="R53" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="S53" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="T53" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="U53" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="S53" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="T53" s="6"/>
-      <c r="U53" s="6"/>
       <c r="V53" s="6"/>
       <c r="W53" s="6"/>
     </row>
-    <row r="54" customHeight="1" ht="72,5">
+    <row r="54" customHeight="1" ht="101,5">
       <c r="A54" s="5" t="n">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>183</v>
@@ -3939,38 +3948,38 @@
         <v>184</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>2000</v>
+        <v>230</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>226</v>
+        <v>110</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O54" s="7" t="n">
-        <v>44791.3073842593</v>
+        <v>44445.4633449074</v>
       </c>
       <c r="P54" s="6"/>
       <c r="Q54" s="7"/>
@@ -3985,53 +3994,55 @@
       <c r="V54" s="6"/>
       <c r="W54" s="6"/>
     </row>
-    <row r="55" customHeight="1" ht="20">
+    <row r="55" customHeight="1" ht="72,5">
       <c r="A55" s="5" t="n">
-        <v>381</v>
+        <v>141</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>186</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I55" s="6"/>
       <c r="J55" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>110</v>
+        <v>226</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N55" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O55" s="7" t="n">
-        <v>45082.6267476852</v>
+        <v>44791.3073842593</v>
       </c>
       <c r="P55" s="6"/>
       <c r="Q55" s="7"/>
-      <c r="R55" s="6"/>
+      <c r="R55" s="6" t="s">
+        <v>188</v>
+      </c>
       <c r="S55" s="6" t="s">
         <v>28</v>
       </c>
@@ -4042,35 +4053,35 @@
     </row>
     <row r="56" customHeight="1" ht="20">
       <c r="A56" s="5" t="n">
-        <v>561</v>
+        <v>381</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L56" s="5" t="n">
         <v>110</v>
@@ -4082,13 +4093,11 @@
         <v>26</v>
       </c>
       <c r="O56" s="7" t="n">
-        <v>45646.6471527778</v>
+        <v>45082.6267476852</v>
       </c>
       <c r="P56" s="6"/>
       <c r="Q56" s="7"/>
-      <c r="R56" s="6" t="s">
-        <v>189</v>
-      </c>
+      <c r="R56" s="6"/>
       <c r="S56" s="6" t="s">
         <v>28</v>
       </c>
@@ -4099,7 +4108,7 @@
     </row>
     <row r="57" customHeight="1" ht="20">
       <c r="A57" s="5" t="n">
-        <v>801</v>
+        <v>561</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>190</v>
@@ -4108,16 +4117,16 @@
         <v>191</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>56</v>
@@ -4127,7 +4136,7 @@
         <v>1</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L57" s="5" t="n">
         <v>110</v>
@@ -4136,14 +4145,16 @@
         <v>10</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="O57" s="7" t="n">
-        <v>45981.747025463</v>
+        <v>45646.6471527778</v>
       </c>
       <c r="P57" s="6"/>
       <c r="Q57" s="7"/>
-      <c r="R57" s="6"/>
+      <c r="R57" s="6" t="s">
+        <v>192</v>
+      </c>
       <c r="S57" s="6" t="s">
         <v>28</v>
       </c>
@@ -4154,32 +4165,32 @@
     </row>
     <row r="58" customHeight="1" ht="20">
       <c r="A58" s="5" t="n">
-        <v>822</v>
+        <v>801</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>56</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K58" s="5" t="n">
         <v>14</v>
@@ -4194,7 +4205,7 @@
         <v>60</v>
       </c>
       <c r="O58" s="7" t="n">
-        <v>45983.3518402778</v>
+        <v>45981.747025463</v>
       </c>
       <c r="P58" s="6"/>
       <c r="Q58" s="7"/>
@@ -4207,55 +4218,53 @@
       <c r="V58" s="6"/>
       <c r="W58" s="6"/>
     </row>
-    <row r="59" customHeight="1" ht="58">
+    <row r="59" customHeight="1" ht="20">
       <c r="A59" s="5" t="n">
-        <v>161</v>
+        <v>822</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I59" s="6"/>
       <c r="J59" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L59" s="5" t="n">
         <v>110</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="O59" s="7" t="n">
-        <v>44807.6812268519</v>
+        <v>45983.3518402778</v>
       </c>
       <c r="P59" s="6"/>
       <c r="Q59" s="7"/>
-      <c r="R59" s="6" t="s">
-        <v>196</v>
-      </c>
+      <c r="R59" s="6"/>
       <c r="S59" s="6" t="s">
         <v>28</v>
       </c>
@@ -4264,9 +4273,9 @@
       <c r="V59" s="6"/>
       <c r="W59" s="6"/>
     </row>
-    <row r="60" customHeight="1" ht="20">
+    <row r="60" customHeight="1" ht="58">
       <c r="A60" s="5" t="n">
-        <v>361</v>
+        <v>161</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>197</v>
@@ -4275,16 +4284,16 @@
         <v>198</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>550</v>
+        <v>120</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>25</v>
@@ -4294,27 +4303,25 @@
         <v>1</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L60" s="5" t="n">
         <v>110</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O60" s="7" t="n">
-        <v>45069</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q60" s="7" t="n">
-        <v>45069.5181018519</v>
-      </c>
-      <c r="R60" s="6"/>
+        <v>44807.6812268519</v>
+      </c>
+      <c r="P60" s="6"/>
+      <c r="Q60" s="7"/>
+      <c r="R60" s="6" t="s">
+        <v>199</v>
+      </c>
       <c r="S60" s="6" t="s">
         <v>28</v>
       </c>
@@ -4325,35 +4332,35 @@
     </row>
     <row r="61" customHeight="1" ht="20">
       <c r="A61" s="5" t="n">
-        <v>681</v>
+        <v>361</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>1200</v>
+        <v>550</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I61" s="6"/>
       <c r="J61" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L61" s="5" t="n">
         <v>110</v>
@@ -4362,16 +4369,18 @@
         <v>10</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="O61" s="7" t="n">
-        <v>45793.6175462963</v>
-      </c>
-      <c r="P61" s="6"/>
-      <c r="Q61" s="7"/>
-      <c r="R61" s="6" t="s">
-        <v>201</v>
-      </c>
+        <v>45069</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q61" s="7" t="n">
+        <v>45069.5181018519</v>
+      </c>
+      <c r="R61" s="6"/>
       <c r="S61" s="6" t="s">
         <v>28</v>
       </c>
@@ -4382,7 +4391,7 @@
     </row>
     <row r="62" customHeight="1" ht="20">
       <c r="A62" s="5" t="n">
-        <v>623</v>
+        <v>681</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>202</v>
@@ -4397,17 +4406,17 @@
         <v>6</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>56</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K62" s="5" t="n">
         <v>14</v>
@@ -4422,7 +4431,7 @@
         <v>60</v>
       </c>
       <c r="O62" s="7" t="n">
-        <v>45700.7507407407</v>
+        <v>45793.6175462963</v>
       </c>
       <c r="P62" s="6"/>
       <c r="Q62" s="7"/>
@@ -4439,7 +4448,7 @@
     </row>
     <row r="63" customHeight="1" ht="20">
       <c r="A63" s="5" t="n">
-        <v>722</v>
+        <v>623</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>205</v>
@@ -4448,16 +4457,16 @@
         <v>206</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F63" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>56</v>
@@ -4479,11 +4488,13 @@
         <v>60</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>45908.4576388889</v>
+        <v>45700.7507407407</v>
       </c>
       <c r="P63" s="6"/>
       <c r="Q63" s="7"/>
-      <c r="R63" s="6"/>
+      <c r="R63" s="6" t="s">
+        <v>207</v>
+      </c>
       <c r="S63" s="6" t="s">
         <v>28</v>
       </c>
@@ -4491,6 +4502,61 @@
       <c r="U63" s="6"/>
       <c r="V63" s="6"/>
       <c r="W63" s="6"/>
+    </row>
+    <row r="64" customHeight="1" ht="20">
+      <c r="A64" s="5" t="n">
+        <v>722</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I64" s="6"/>
+      <c r="J64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="O64" s="7" t="n">
+        <v>45908.4576388889</v>
+      </c>
+      <c r="P64" s="6"/>
+      <c r="Q64" s="7"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="T64" s="6"/>
+      <c r="U64" s="6"/>
+      <c r="V64" s="6"/>
+      <c r="W64" s="6"/>
     </row>
   </sheetData>
   <tableParts count="1">

--- a/inp_Excel/ana_viaggi.xlsx
+++ b/inp_Excel/ana_viaggi.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="207">
   <si>
     <t>VIAGGIO_ID</t>
   </si>
@@ -655,15 +655,6 @@
   </si>
   <si>
     <t>https://www.sardegnafuoritraccia.it/it/tour/moto-enduro/maxi-enduro-tour-gpx-sardegna-2025</t>
-  </si>
-  <si>
-    <t>ICHNUSA TOUR 4X4</t>
-  </si>
-  <si>
-    <t>GIRO DELLA SARDEGNA IN FUORISTRADA</t>
-  </si>
-  <si>
-    <t>https://www.sardegnafuoritraccia.it/it/tour/fuoristrada/ichnusa-tour-4x4</t>
   </si>
   <si>
     <t>CAPODANNO IN FUORISTRADA 8 GG</t>
@@ -769,8 +760,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:W64" totalsRowShown="0" headerRowCount="1">
-  <autoFilter ref="A1:W64"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:W63" totalsRowShown="0" headerRowCount="1">
+  <autoFilter ref="A1:W63"/>
   <tableColumns count="23">
     <tableColumn id="1" name="VIAGGIO_ID"/>
     <tableColumn id="2" name="VIAGGIO_DESCRIZIONE_BREVE"/>
@@ -4448,7 +4439,7 @@
     </row>
     <row r="63" customHeight="1" ht="20">
       <c r="A63" s="5" t="n">
-        <v>623</v>
+        <v>722</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>205</v>
@@ -4457,16 +4448,16 @@
         <v>206</v>
       </c>
       <c r="D63" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E63" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="F63" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>56</v>
@@ -4488,13 +4479,11 @@
         <v>60</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>45700.7507407407</v>
+        <v>45908.4576388889</v>
       </c>
       <c r="P63" s="6"/>
       <c r="Q63" s="7"/>
-      <c r="R63" s="6" t="s">
-        <v>207</v>
-      </c>
+      <c r="R63" s="6"/>
       <c r="S63" s="6" t="s">
         <v>28</v>
       </c>
@@ -4502,61 +4491,6 @@
       <c r="U63" s="6"/>
       <c r="V63" s="6"/>
       <c r="W63" s="6"/>
-    </row>
-    <row r="64" customHeight="1" ht="20">
-      <c r="A64" s="5" t="n">
-        <v>722</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="D64" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I64" s="6"/>
-      <c r="J64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="N64" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="O64" s="7" t="n">
-        <v>45908.4576388889</v>
-      </c>
-      <c r="P64" s="6"/>
-      <c r="Q64" s="7"/>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
-      <c r="V64" s="6"/>
-      <c r="W64" s="6"/>
     </row>
   </sheetData>
   <tableParts count="1">

--- a/inp_Excel/ana_viaggi.xlsx
+++ b/inp_Excel/ana_viaggi.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="213">
   <si>
     <t>VIAGGIO_ID</t>
   </si>
@@ -203,6 +203,15 @@
     <t>https://www.sardegnafuoritraccia.it/it/tour/fuoristrada/dalle-dune-alla-gallura-settembre-4x4</t>
   </si>
   <si>
+    <t>PRIMAVERA IN OGLIASTRA</t>
+  </si>
+  <si>
+    <t>Un viaggio nella bellissima e selvaggia ogliastra</t>
+  </si>
+  <si>
+    <t>https://www.sardegnafuoritraccia.it/it/tour/fuoristrada/primavera-ogliastra-4x4</t>
+  </si>
+  <si>
     <t>4X4 - BAGNO VIGNONI - GUBBIO</t>
   </si>
   <si>
@@ -398,6 +407,15 @@
     <t>https://www.sardegnafuoritraccia.it/it/tour/fuoristrada-estero/nord-portugal-4x4</t>
   </si>
   <si>
+    <t>MAXI ENDURO TOUR DEI 2 MARI</t>
+  </si>
+  <si>
+    <t>Un viaggio con la maxi enduro da ovest a est dell'isola passando per la barbagia</t>
+  </si>
+  <si>
+    <t>https://www.sardegnafuoritraccia.it/it/tour/moto-enduro/maxi-tour-dei-2-mari</t>
+  </si>
+  <si>
     <t>4X4 - BALCANI ADVENTURE</t>
   </si>
   <si>
@@ -521,7 +539,7 @@
     <t>https://www.sardegnafuoritraccia.it/it/tour/fuoristrada/wild-tour-sardegna-4x4</t>
   </si>
   <si>
-    <t>NISSAN TERRANO TOUR</t>
+    <t>EST SARDEGNA IN 4X4</t>
   </si>
   <si>
     <t>dalla gallura al cuore della sardegna, passando per il mare cristallino dell'ogliastra</t>
@@ -625,7 +643,7 @@
     <t>il giro della sardegna in fuoristrada</t>
   </si>
   <si>
-    <t>GRAN TOUR ENDURO GENNAIO</t>
+    <t>GRAN TOUR ENDURO FEBBRAIO</t>
   </si>
   <si>
     <t>3 GIORNI DI ENDURO IN SARDEGNA</t>
@@ -760,8 +778,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:W63" totalsRowShown="0" headerRowCount="1">
-  <autoFilter ref="A1:W63"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:W65" totalsRowShown="0" headerRowCount="1">
+  <autoFilter ref="A1:W65"/>
   <tableColumns count="23">
     <tableColumn id="1" name="VIAGGIO_ID"/>
     <tableColumn id="2" name="VIAGGIO_DESCRIZIONE_BREVE"/>
@@ -1594,7 +1612,7 @@
     </row>
     <row r="14" customHeight="1" ht="20">
       <c r="A14" s="5" t="n">
-        <v>22</v>
+        <v>881</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>62</v>
@@ -1603,26 +1621,26 @@
         <v>63</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>110</v>
@@ -1631,10 +1649,10 @@
         <v>10</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>44420.4137037037</v>
+        <v>46049.8503935185</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="7"/>
@@ -1644,39 +1662,35 @@
       <c r="S14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="T14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="U14" s="6" t="s">
-        <v>65</v>
-      </c>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
       <c r="V14" s="6"/>
       <c r="W14" s="6"/>
     </row>
     <row r="15" customHeight="1" ht="20">
       <c r="A15" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>650</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="5" t="n">
@@ -1686,7 +1700,7 @@
         <v>13</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>10</v>
@@ -1695,24 +1709,28 @@
         <v>26</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>44420.4427314815</v>
+        <v>44420.4137037037</v>
       </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="S15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="T15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="U15" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="S15" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
       <c r="V15" s="6"/>
       <c r="W15" s="6"/>
     </row>
     <row r="16" customHeight="1" ht="20">
       <c r="A16" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>69</v>
@@ -1721,29 +1739,29 @@
         <v>70</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>300</v>
+        <v>650</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="M16" s="5" t="n">
         <v>10</v>
@@ -1752,14 +1770,10 @@
         <v>26</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>44420</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q16" s="7" t="n">
-        <v>45089.7977777778</v>
-      </c>
+        <v>44420.4427314815</v>
+      </c>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="7"/>
       <c r="R16" s="6" t="s">
         <v>71</v>
       </c>
@@ -1771,9 +1785,9 @@
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
     </row>
-    <row r="17" customHeight="1" ht="72,5">
+    <row r="17" customHeight="1" ht="20">
       <c r="A17" s="5" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>72</v>
@@ -1782,80 +1796,80 @@
         <v>73</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N17" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>44445.4405902778</v>
-      </c>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="7"/>
+        <v>44420</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q17" s="7" t="n">
+        <v>45089.7977777778</v>
+      </c>
       <c r="R17" s="6" t="s">
         <v>74</v>
       </c>
       <c r="S17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="T17" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="U17" s="6" t="s">
-        <v>75</v>
-      </c>
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
       <c r="V17" s="6"/>
       <c r="W17" s="6"/>
     </row>
-    <row r="18" customHeight="1" ht="29">
+    <row r="18" customHeight="1" ht="72,5">
       <c r="A18" s="5" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="D18" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>590</v>
+        <v>1200</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="5" t="n">
@@ -1865,21 +1879,21 @@
         <v>13</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>44445.4494328704</v>
+        <v>44445.4405902778</v>
       </c>
       <c r="P18" s="6"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S18" s="6" t="s">
         <v>28</v>
@@ -1888,32 +1902,32 @@
         <v>29</v>
       </c>
       <c r="U18" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="V18" s="6"/>
       <c r="W18" s="6"/>
     </row>
     <row r="19" customHeight="1" ht="29">
       <c r="A19" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>81</v>
-      </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>240</v>
+        <v>590</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>25</v>
@@ -1935,12 +1949,12 @@
         <v>26</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>44445.451400463</v>
+        <v>44445.4494328704</v>
       </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S19" s="6" t="s">
         <v>28</v>
@@ -1949,32 +1963,32 @@
         <v>29</v>
       </c>
       <c r="U19" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V19" s="6"/>
       <c r="W19" s="6"/>
     </row>
-    <row r="20" customHeight="1" ht="20">
+    <row r="20" customHeight="1" ht="29">
       <c r="A20" s="5" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>85</v>
-      </c>
       <c r="D20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>25</v>
@@ -1984,28 +1998,24 @@
         <v>1</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>110</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>44445</v>
-      </c>
-      <c r="P20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q20" s="7" t="n">
-        <v>44445.4601967593</v>
-      </c>
+        <v>44445.451400463</v>
+      </c>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="7"/>
       <c r="R20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S20" s="6" t="s">
         <v>28</v>
@@ -2014,32 +2024,32 @@
         <v>29</v>
       </c>
       <c r="U20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="V20" s="6"/>
       <c r="W20" s="6"/>
     </row>
-    <row r="21" customHeight="1" ht="29">
+    <row r="21" customHeight="1" ht="20">
       <c r="A21" s="5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>89</v>
-      </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>260</v>
+        <v>125</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>25</v>
@@ -2049,36 +2059,44 @@
         <v>1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L21" s="5" t="n">
         <v>110</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N21" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>44445.456875</v>
-      </c>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="7"/>
+        <v>44445</v>
+      </c>
+      <c r="P21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="7" t="n">
+        <v>44445.4601967593</v>
+      </c>
       <c r="R21" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="S21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="T21" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="U21" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="S21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="T21" s="6"/>
-      <c r="U21" s="6"/>
       <c r="V21" s="6"/>
       <c r="W21" s="6"/>
     </row>
-    <row r="22" customHeight="1" ht="58">
+    <row r="22" customHeight="1" ht="29">
       <c r="A22" s="5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>91</v>
@@ -2087,16 +2105,16 @@
         <v>92</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>450</v>
+        <v>260</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>25</v>
@@ -2118,7 +2136,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>44445.458275463</v>
+        <v>44445.456875</v>
       </c>
       <c r="P22" s="6"/>
       <c r="Q22" s="7"/>
@@ -2133,15 +2151,15 @@
       <c r="V22" s="6"/>
       <c r="W22" s="6"/>
     </row>
-    <row r="23" customHeight="1" ht="20">
+    <row r="23" customHeight="1" ht="58">
       <c r="A23" s="5" t="n">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>94</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>4</v>
@@ -2153,7 +2171,7 @@
         <v>24</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>25</v>
@@ -2175,11 +2193,13 @@
         <v>26</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>44645.3951967593</v>
+        <v>44445.458275463</v>
       </c>
       <c r="P23" s="6"/>
       <c r="Q23" s="7"/>
-      <c r="R23" s="6"/>
+      <c r="R23" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="S23" s="6" t="s">
         <v>28</v>
       </c>
@@ -2190,25 +2210,25 @@
     </row>
     <row r="24" customHeight="1" ht="20">
       <c r="A24" s="5" t="n">
-        <v>261</v>
+        <v>121</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E24" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="F24" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>25</v>
@@ -2218,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>110</v>
@@ -2230,14 +2250,10 @@
         <v>26</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>45000</v>
-      </c>
-      <c r="P24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q24" s="7" t="n">
-        <v>45069.5184722222</v>
-      </c>
+        <v>44645.3951967593</v>
+      </c>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="7"/>
       <c r="R24" s="6"/>
       <c r="S24" s="6" t="s">
         <v>28</v>
@@ -2249,25 +2265,25 @@
     </row>
     <row r="25" customHeight="1" ht="20">
       <c r="A25" s="5" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>25</v>
@@ -2277,7 +2293,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L25" s="5" t="n">
         <v>110</v>
@@ -2289,10 +2305,14 @@
         <v>26</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>45032.5716319444</v>
-      </c>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="7"/>
+        <v>45000</v>
+      </c>
+      <c r="P25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>45069.5184722222</v>
+      </c>
       <c r="R25" s="6"/>
       <c r="S25" s="6" t="s">
         <v>28</v>
@@ -2304,38 +2324,38 @@
     </row>
     <row r="26" customHeight="1" ht="20">
       <c r="A26" s="5" t="n">
-        <v>321</v>
+        <v>281</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1600</v>
+        <v>500</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="M26" s="5" t="n">
         <v>10</v>
@@ -2344,7 +2364,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>45042.6747222222</v>
+        <v>45032.5716319444</v>
       </c>
       <c r="P26" s="6"/>
       <c r="Q26" s="7"/>
@@ -2357,40 +2377,40 @@
       <c r="V26" s="6"/>
       <c r="W26" s="6"/>
     </row>
-    <row r="27" customHeight="1" ht="116">
+    <row r="27" customHeight="1" ht="20">
       <c r="A27" s="5" t="n">
-        <v>401</v>
+        <v>321</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I27" s="6"/>
       <c r="J27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>209</v>
+        <v>34</v>
       </c>
       <c r="M27" s="5" t="n">
         <v>10</v>
@@ -2399,13 +2419,11 @@
         <v>26</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>45111.2530902778</v>
+        <v>45042.6747222222</v>
       </c>
       <c r="P27" s="6"/>
       <c r="Q27" s="7"/>
-      <c r="R27" s="6" t="s">
-        <v>103</v>
-      </c>
+      <c r="R27" s="6"/>
       <c r="S27" s="6" t="s">
         <v>28</v>
       </c>
@@ -2414,27 +2432,27 @@
       <c r="V27" s="6"/>
       <c r="W27" s="6"/>
     </row>
-    <row r="28" customHeight="1" ht="20">
+    <row r="28" customHeight="1" ht="116">
       <c r="A28" s="5" t="n">
-        <v>441</v>
+        <v>401</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>104</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>25</v>
@@ -2447,7 +2465,7 @@
         <v>13</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="M28" s="5" t="n">
         <v>10</v>
@@ -2456,11 +2474,13 @@
         <v>26</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>45277.4562615741</v>
+        <v>45111.2530902778</v>
       </c>
       <c r="P28" s="6"/>
       <c r="Q28" s="7"/>
-      <c r="R28" s="6"/>
+      <c r="R28" s="6" t="s">
+        <v>106</v>
+      </c>
       <c r="S28" s="6" t="s">
         <v>28</v>
       </c>
@@ -2469,27 +2489,27 @@
       <c r="V28" s="6"/>
       <c r="W28" s="6"/>
     </row>
-    <row r="29" customHeight="1" ht="29">
+    <row r="29" customHeight="1" ht="20">
       <c r="A29" s="5" t="n">
-        <v>501</v>
+        <v>441</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>25</v>
@@ -2511,13 +2531,11 @@
         <v>26</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>45310.3687152778</v>
+        <v>45277.4562615741</v>
       </c>
       <c r="P29" s="6"/>
       <c r="Q29" s="7"/>
-      <c r="R29" s="6" t="s">
-        <v>107</v>
-      </c>
+      <c r="R29" s="6"/>
       <c r="S29" s="6" t="s">
         <v>28</v>
       </c>
@@ -2526,9 +2544,9 @@
       <c r="V29" s="6"/>
       <c r="W29" s="6"/>
     </row>
-    <row r="30" customHeight="1" ht="43,5">
+    <row r="30" customHeight="1" ht="29">
       <c r="A30" s="5" t="n">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>108</v>
@@ -2537,19 +2555,19 @@
         <v>109</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1500</v>
+        <v>350</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I30" s="6"/>
       <c r="J30" s="5" t="n">
@@ -2559,7 +2577,7 @@
         <v>13</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>227</v>
+        <v>110</v>
       </c>
       <c r="M30" s="5" t="n">
         <v>10</v>
@@ -2568,7 +2586,7 @@
         <v>26</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>45348.3882060185</v>
+        <v>45310.3687152778</v>
       </c>
       <c r="P30" s="6"/>
       <c r="Q30" s="7"/>
@@ -2583,9 +2601,9 @@
       <c r="V30" s="6"/>
       <c r="W30" s="6"/>
     </row>
-    <row r="31" customHeight="1" ht="20">
+    <row r="31" customHeight="1" ht="43,5">
       <c r="A31" s="5" t="n">
-        <v>621</v>
+        <v>521</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>111</v>
@@ -2594,16 +2612,16 @@
         <v>112</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>56</v>
@@ -2613,26 +2631,22 @@
         <v>1</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="M31" s="5" t="n">
         <v>10</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>45700</v>
-      </c>
-      <c r="P31" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q31" s="7" t="n">
-        <v>45908.4513194444</v>
-      </c>
+        <v>45348.3882060185</v>
+      </c>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="7"/>
       <c r="R31" s="6" t="s">
         <v>113</v>
       </c>
@@ -2646,7 +2660,7 @@
     </row>
     <row r="32" customHeight="1" ht="20">
       <c r="A32" s="5" t="n">
-        <v>762</v>
+        <v>621</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>114</v>
@@ -2664,7 +2678,7 @@
         <v>24</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>860</v>
+        <v>800</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>56</v>
@@ -2686,15 +2700,17 @@
         <v>60</v>
       </c>
       <c r="O32" s="7" t="n">
-        <v>45963</v>
+        <v>45700</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>60</v>
       </c>
       <c r="Q32" s="7" t="n">
-        <v>45963.342974537</v>
-      </c>
-      <c r="R32" s="6"/>
+        <v>45908.4513194444</v>
+      </c>
+      <c r="R32" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="S32" s="6" t="s">
         <v>28</v>
       </c>
@@ -2705,53 +2721,55 @@
     </row>
     <row r="33" customHeight="1" ht="20">
       <c r="A33" s="5" t="n">
-        <v>626</v>
+        <v>762</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>1400</v>
+        <v>860</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I33" s="6"/>
       <c r="J33" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>60</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>45700.7545717593</v>
-      </c>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="6" t="s">
-        <v>118</v>
-      </c>
+        <v>45963</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>45963.342974537</v>
+      </c>
+      <c r="R33" s="6"/>
       <c r="S33" s="6" t="s">
         <v>28</v>
       </c>
@@ -2762,7 +2780,7 @@
     </row>
     <row r="34" customHeight="1" ht="20">
       <c r="A34" s="5" t="n">
-        <v>821</v>
+        <v>626</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>119</v>
@@ -2771,42 +2789,44 @@
         <v>120</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I34" s="6"/>
       <c r="J34" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>60</v>
       </c>
       <c r="O34" s="7" t="n">
-        <v>45983.3453356481</v>
+        <v>45700.7545717593</v>
       </c>
       <c r="P34" s="6"/>
       <c r="Q34" s="7"/>
-      <c r="R34" s="6"/>
+      <c r="R34" s="6" t="s">
+        <v>121</v>
+      </c>
       <c r="S34" s="6" t="s">
         <v>28</v>
       </c>
@@ -2817,38 +2837,38 @@
     </row>
     <row r="35" customHeight="1" ht="20">
       <c r="A35" s="5" t="n">
-        <v>861</v>
+        <v>821</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K35" s="5" t="n">
         <v>14</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="M35" s="5" t="n">
         <v>10</v>
@@ -2857,13 +2877,11 @@
         <v>60</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>46031.304849537</v>
+        <v>45983.3453356481</v>
       </c>
       <c r="P35" s="6"/>
       <c r="Q35" s="7"/>
-      <c r="R35" s="6" t="s">
-        <v>123</v>
-      </c>
+      <c r="R35" s="6"/>
       <c r="S35" s="6" t="s">
         <v>28</v>
       </c>
@@ -2874,7 +2892,7 @@
     </row>
     <row r="36" customHeight="1" ht="20">
       <c r="A36" s="5" t="n">
-        <v>23</v>
+        <v>861</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>124</v>
@@ -2883,19 +2901,19 @@
         <v>125</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I36" s="6"/>
       <c r="J36" s="5" t="n">
@@ -2905,16 +2923,16 @@
         <v>14</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="O36" s="7" t="n">
-        <v>44420.4166319444</v>
+        <v>46031.304849537</v>
       </c>
       <c r="P36" s="6"/>
       <c r="Q36" s="7"/>
@@ -2924,97 +2942,93 @@
       <c r="S36" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="T36" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="U36" s="6" t="s">
-        <v>127</v>
-      </c>
+      <c r="T36" s="6"/>
+      <c r="U36" s="6"/>
       <c r="V36" s="6"/>
       <c r="W36" s="6"/>
     </row>
     <row r="37" customHeight="1" ht="20">
       <c r="A37" s="5" t="n">
-        <v>24</v>
+        <v>901</v>
       </c>
       <c r="B37" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="D37" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E37" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="F37" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>304</v>
+        <v>800</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>56</v>
       </c>
       <c r="I37" s="6"/>
       <c r="J37" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K37" s="5" t="n">
         <v>14</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="M37" s="5" t="n">
         <v>10</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>44420.4193634259</v>
-      </c>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="7"/>
+        <v>46053</v>
+      </c>
+      <c r="P37" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q37" s="7" t="n">
+        <v>46053.8134027778</v>
+      </c>
       <c r="R37" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S37" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="T37" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="U37" s="6" t="s">
-        <v>131</v>
-      </c>
+      <c r="T37" s="6"/>
+      <c r="U37" s="6"/>
       <c r="V37" s="6"/>
       <c r="W37" s="6"/>
     </row>
-    <row r="38" customHeight="1" ht="29">
+    <row r="38" customHeight="1" ht="20">
       <c r="A38" s="5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>1000</v>
+        <v>1700</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>56</v>
@@ -3024,24 +3038,24 @@
         <v>1</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>2</v>
+        <v>146</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O38" s="7" t="n">
-        <v>44420.5078125</v>
+        <v>44420.4166319444</v>
       </c>
       <c r="P38" s="6"/>
       <c r="Q38" s="7"/>
       <c r="R38" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="S38" s="6" t="s">
         <v>28</v>
@@ -3050,20 +3064,20 @@
         <v>29</v>
       </c>
       <c r="U38" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="V38" s="6"/>
       <c r="W38" s="6"/>
     </row>
     <row r="39" customHeight="1" ht="20">
       <c r="A39" s="5" t="n">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>3</v>
@@ -3072,23 +3086,23 @@
         <v>2</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>350</v>
+        <v>304</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I39" s="6"/>
       <c r="J39" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="M39" s="5" t="n">
         <v>10</v>
@@ -3097,53 +3111,59 @@
         <v>26</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>44468.751412037</v>
+        <v>44420.4193634259</v>
       </c>
       <c r="P39" s="6"/>
       <c r="Q39" s="7"/>
-      <c r="R39" s="6"/>
+      <c r="R39" s="6" t="s">
+        <v>136</v>
+      </c>
       <c r="S39" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
+      <c r="T39" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="U39" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="V39" s="6"/>
       <c r="W39" s="6"/>
     </row>
-    <row r="40" customHeight="1" ht="43,5">
+    <row r="40" customHeight="1" ht="29">
       <c r="A40" s="5" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>205</v>
+        <v>1000</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="M40" s="5" t="n">
         <v>10</v>
@@ -3152,18 +3172,18 @@
         <v>26</v>
       </c>
       <c r="O40" s="7" t="n">
-        <v>44594.3402662037</v>
+        <v>44420.5078125</v>
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="7"/>
       <c r="R40" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="S40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="T40" s="6" t="s">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="U40" s="6" t="s">
         <v>141</v>
@@ -3171,34 +3191,34 @@
       <c r="V40" s="6"/>
       <c r="W40" s="6"/>
     </row>
-    <row r="41" customHeight="1" ht="29">
+    <row r="41" customHeight="1" ht="20">
       <c r="A41" s="5" t="n">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>142</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D41" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E41" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F41" s="6" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>230</v>
+        <v>350</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I41" s="6"/>
       <c r="J41" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K41" s="5" t="n">
         <v>13</v>
@@ -3213,34 +3233,28 @@
         <v>26</v>
       </c>
       <c r="O41" s="7" t="n">
-        <v>44615.8342361111</v>
+        <v>44468.751412037</v>
       </c>
       <c r="P41" s="6"/>
       <c r="Q41" s="7"/>
-      <c r="R41" s="6" t="s">
-        <v>144</v>
-      </c>
+      <c r="R41" s="6"/>
       <c r="S41" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="T41" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="U41" s="6" t="s">
-        <v>145</v>
-      </c>
+      <c r="T41" s="6"/>
+      <c r="U41" s="6"/>
       <c r="V41" s="6"/>
       <c r="W41" s="6"/>
     </row>
-    <row r="42" customHeight="1" ht="87">
+    <row r="42" customHeight="1" ht="43,5">
       <c r="A42" s="5" t="n">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>2</v>
@@ -3252,7 +3266,7 @@
         <v>24</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>25</v>
@@ -3274,34 +3288,34 @@
         <v>26</v>
       </c>
       <c r="O42" s="7" t="n">
-        <v>44810.5888425926</v>
+        <v>44594.3402662037</v>
       </c>
       <c r="P42" s="6"/>
       <c r="Q42" s="7"/>
       <c r="R42" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="S42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="T42" s="6" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="U42" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="V42" s="6"/>
       <c r="W42" s="6"/>
     </row>
-    <row r="43" customHeight="1" ht="43,5">
+    <row r="43" customHeight="1" ht="29">
       <c r="A43" s="5" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>2</v>
@@ -3313,7 +3327,7 @@
         <v>24</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>25</v>
@@ -3335,56 +3349,56 @@
         <v>26</v>
       </c>
       <c r="O43" s="7" t="n">
-        <v>44834.2956712963</v>
+        <v>44615.8342361111</v>
       </c>
       <c r="P43" s="6"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="S43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="T43" s="6" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="U43" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
     </row>
-    <row r="44" customHeight="1" ht="43,5">
+    <row r="44" customHeight="1" ht="87">
       <c r="A44" s="5" t="n">
-        <v>741</v>
+        <v>181</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>650</v>
+        <v>210</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L44" s="5" t="n">
         <v>110</v>
@@ -3393,55 +3407,59 @@
         <v>10</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="O44" s="7" t="n">
-        <v>45951.6437962963</v>
+        <v>44810.5888425926</v>
       </c>
       <c r="P44" s="6"/>
       <c r="Q44" s="7"/>
       <c r="R44" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="S44" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="T44" s="6"/>
-      <c r="U44" s="6"/>
+      <c r="T44" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="U44" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="V44" s="6"/>
       <c r="W44" s="6"/>
     </row>
-    <row r="45" customHeight="1" ht="20">
+    <row r="45" customHeight="1" ht="43,5">
       <c r="A45" s="5" t="n">
-        <v>622</v>
+        <v>201</v>
       </c>
       <c r="B45" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>158</v>
-      </c>
       <c r="D45" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>650</v>
+        <v>240</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I45" s="6"/>
       <c r="J45" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L45" s="5" t="n">
         <v>110</v>
@@ -3450,27 +3468,31 @@
         <v>10</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>45700.7497453704</v>
+        <v>44834.2956712963</v>
       </c>
       <c r="P45" s="6"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="S45" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="T45" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="U45" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="S45" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="T45" s="6"/>
-      <c r="U45" s="6"/>
       <c r="V45" s="6"/>
       <c r="W45" s="6"/>
     </row>
-    <row r="46" customHeight="1" ht="20">
+    <row r="46" customHeight="1" ht="43,5">
       <c r="A46" s="5" t="n">
-        <v>624</v>
+        <v>741</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>160</v>
@@ -3488,7 +3510,7 @@
         <v>24</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>56</v>
@@ -3498,19 +3520,19 @@
         <v>1</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>110</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>60</v>
       </c>
       <c r="O46" s="7" t="n">
-        <v>45700.7520138889</v>
+        <v>45951.6437962963</v>
       </c>
       <c r="P46" s="6"/>
       <c r="Q46" s="7"/>
@@ -3527,7 +3549,7 @@
     </row>
     <row r="47" customHeight="1" ht="20">
       <c r="A47" s="5" t="n">
-        <v>761</v>
+        <v>622</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>163</v>
@@ -3545,7 +3567,7 @@
         <v>24</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1000</v>
+        <v>650</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>56</v>
@@ -3567,11 +3589,13 @@
         <v>60</v>
       </c>
       <c r="O47" s="7" t="n">
-        <v>45963.3376273148</v>
+        <v>45700.7497453704</v>
       </c>
       <c r="P47" s="6"/>
       <c r="Q47" s="7"/>
-      <c r="R47" s="6"/>
+      <c r="R47" s="6" t="s">
+        <v>165</v>
+      </c>
       <c r="S47" s="6" t="s">
         <v>28</v>
       </c>
@@ -3582,25 +3606,25 @@
     </row>
     <row r="48" customHeight="1" ht="20">
       <c r="A48" s="5" t="n">
-        <v>781</v>
+        <v>624</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>880</v>
+        <v>600</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>56</v>
@@ -3610,23 +3634,25 @@
         <v>1</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L48" s="5" t="n">
         <v>110</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>60</v>
       </c>
       <c r="O48" s="7" t="n">
-        <v>45964.9283101852</v>
+        <v>45700.7520138889</v>
       </c>
       <c r="P48" s="6"/>
       <c r="Q48" s="7"/>
-      <c r="R48" s="6"/>
+      <c r="R48" s="6" t="s">
+        <v>168</v>
+      </c>
       <c r="S48" s="6" t="s">
         <v>28</v>
       </c>
@@ -3635,27 +3661,27 @@
       <c r="V48" s="6"/>
       <c r="W48" s="6"/>
     </row>
-    <row r="49" customHeight="1" ht="29">
+    <row r="49" customHeight="1" ht="20">
       <c r="A49" s="5" t="n">
-        <v>42</v>
+        <v>761</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2300</v>
+        <v>1000</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>56</v>
@@ -3665,25 +3691,27 @@
         <v>1</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="M49" s="5" t="n">
         <v>10</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="O49" s="7" t="n">
-        <v>44445.445150463</v>
-      </c>
-      <c r="P49" s="6"/>
-      <c r="Q49" s="7"/>
-      <c r="R49" s="6" t="s">
-        <v>169</v>
-      </c>
+        <v>45963</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q49" s="7" t="n">
+        <v>46082.7516782407</v>
+      </c>
+      <c r="R49" s="6"/>
       <c r="S49" s="6" t="s">
         <v>28</v>
       </c>
@@ -3692,37 +3720,37 @@
       <c r="V49" s="6"/>
       <c r="W49" s="6"/>
     </row>
-    <row r="50" customHeight="1" ht="43,5">
+    <row r="50" customHeight="1" ht="20">
       <c r="A50" s="5" t="n">
-        <v>43</v>
+        <v>781</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>600</v>
+        <v>880</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L50" s="5" t="n">
         <v>110</v>
@@ -3731,16 +3759,14 @@
         <v>10</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="O50" s="7" t="n">
-        <v>44445.4470717593</v>
+        <v>45964.9283101852</v>
       </c>
       <c r="P50" s="6"/>
       <c r="Q50" s="7"/>
-      <c r="R50" s="6" t="s">
-        <v>172</v>
-      </c>
+      <c r="R50" s="6"/>
       <c r="S50" s="6" t="s">
         <v>28</v>
       </c>
@@ -3751,7 +3777,7 @@
     </row>
     <row r="51" customHeight="1" ht="29">
       <c r="A51" s="5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>173</v>
@@ -3760,19 +3786,19 @@
         <v>174</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>600</v>
+        <v>2300</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I51" s="6"/>
       <c r="J51" s="5" t="n">
@@ -3782,7 +3808,7 @@
         <v>13</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="M51" s="5" t="n">
         <v>10</v>
@@ -3791,14 +3817,10 @@
         <v>26</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>44445</v>
-      </c>
-      <c r="P51" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q51" s="7" t="n">
-        <v>45479.6319907407</v>
-      </c>
+        <v>44445.445150463</v>
+      </c>
+      <c r="P51" s="6"/>
+      <c r="Q51" s="7"/>
       <c r="R51" s="6" t="s">
         <v>175</v>
       </c>
@@ -3810,9 +3832,9 @@
       <c r="V51" s="6"/>
       <c r="W51" s="6"/>
     </row>
-    <row r="52" customHeight="1" ht="72,5">
+    <row r="52" customHeight="1" ht="43,5">
       <c r="A52" s="5" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>176</v>
@@ -3821,16 +3843,16 @@
         <v>177</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>280</v>
+        <v>600</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>25</v>
@@ -3852,7 +3874,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="7" t="n">
-        <v>44445.4529976852</v>
+        <v>44445.4470717593</v>
       </c>
       <c r="P52" s="6"/>
       <c r="Q52" s="7"/>
@@ -3867,9 +3889,9 @@
       <c r="V52" s="6"/>
       <c r="W52" s="6"/>
     </row>
-    <row r="53" customHeight="1" ht="43,5">
+    <row r="53" customHeight="1" ht="29">
       <c r="A53" s="5" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>179</v>
@@ -3878,16 +3900,16 @@
         <v>180</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>140</v>
+        <v>600</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>25</v>
@@ -3897,46 +3919,46 @@
         <v>1</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L53" s="5" t="n">
         <v>110</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N53" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O53" s="7" t="n">
-        <v>44445.4599768519</v>
-      </c>
-      <c r="P53" s="6"/>
-      <c r="Q53" s="7"/>
+        <v>44445</v>
+      </c>
+      <c r="P53" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q53" s="7" t="n">
+        <v>45479.6319907407</v>
+      </c>
       <c r="R53" s="6" t="s">
         <v>181</v>
       </c>
       <c r="S53" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="T53" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="U53" s="6" t="s">
-        <v>182</v>
-      </c>
+      <c r="T53" s="6"/>
+      <c r="U53" s="6"/>
       <c r="V53" s="6"/>
       <c r="W53" s="6"/>
     </row>
-    <row r="54" customHeight="1" ht="101,5">
+    <row r="54" customHeight="1" ht="72,5">
       <c r="A54" s="5" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B54" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C54" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>2</v>
@@ -3948,7 +3970,7 @@
         <v>24</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>25</v>
@@ -3970,12 +3992,12 @@
         <v>26</v>
       </c>
       <c r="O54" s="7" t="n">
-        <v>44445.4633449074</v>
+        <v>44445.4529976852</v>
       </c>
       <c r="P54" s="6"/>
       <c r="Q54" s="7"/>
       <c r="R54" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S54" s="6" t="s">
         <v>28</v>
@@ -3985,72 +4007,76 @@
       <c r="V54" s="6"/>
       <c r="W54" s="6"/>
     </row>
-    <row r="55" customHeight="1" ht="72,5">
+    <row r="55" customHeight="1" ht="43,5">
       <c r="A55" s="5" t="n">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="B55" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C55" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>187</v>
-      </c>
       <c r="D55" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>49</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>2000</v>
+        <v>140</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I55" s="6"/>
       <c r="J55" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>226</v>
+        <v>110</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N55" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O55" s="7" t="n">
-        <v>44791.3073842593</v>
+        <v>44445.4599768519</v>
       </c>
       <c r="P55" s="6"/>
       <c r="Q55" s="7"/>
       <c r="R55" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="S55" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="T55" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="U55" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="S55" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
       <c r="V55" s="6"/>
       <c r="W55" s="6"/>
     </row>
-    <row r="56" customHeight="1" ht="20">
+    <row r="56" customHeight="1" ht="101,5">
       <c r="A56" s="5" t="n">
-        <v>381</v>
+        <v>54</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>189</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>2</v>
@@ -4062,7 +4088,7 @@
         <v>24</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>25</v>
@@ -4084,11 +4110,13 @@
         <v>26</v>
       </c>
       <c r="O56" s="7" t="n">
-        <v>45082.6267476852</v>
+        <v>44445.4633449074</v>
       </c>
       <c r="P56" s="6"/>
       <c r="Q56" s="7"/>
-      <c r="R56" s="6"/>
+      <c r="R56" s="6" t="s">
+        <v>191</v>
+      </c>
       <c r="S56" s="6" t="s">
         <v>28</v>
       </c>
@@ -4097,27 +4125,27 @@
       <c r="V56" s="6"/>
       <c r="W56" s="6"/>
     </row>
-    <row r="57" customHeight="1" ht="20">
+    <row r="57" customHeight="1" ht="72,5">
       <c r="A57" s="5" t="n">
-        <v>561</v>
+        <v>141</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>49</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>56</v>
@@ -4127,24 +4155,24 @@
         <v>1</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>110</v>
+        <v>226</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N57" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O57" s="7" t="n">
-        <v>45646.6471527778</v>
+        <v>44791.3073842593</v>
       </c>
       <c r="P57" s="6"/>
       <c r="Q57" s="7"/>
       <c r="R57" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="S57" s="6" t="s">
         <v>28</v>
@@ -4156,35 +4184,35 @@
     </row>
     <row r="58" customHeight="1" ht="20">
       <c r="A58" s="5" t="n">
-        <v>801</v>
+        <v>381</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>1200</v>
+        <v>250</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L58" s="5" t="n">
         <v>110</v>
@@ -4193,10 +4221,10 @@
         <v>10</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="O58" s="7" t="n">
-        <v>45981.747025463</v>
+        <v>45082.6267476852</v>
       </c>
       <c r="P58" s="6"/>
       <c r="Q58" s="7"/>
@@ -4211,35 +4239,35 @@
     </row>
     <row r="59" customHeight="1" ht="20">
       <c r="A59" s="5" t="n">
-        <v>822</v>
+        <v>561</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>56</v>
       </c>
       <c r="I59" s="6"/>
       <c r="J59" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L59" s="5" t="n">
         <v>110</v>
@@ -4248,14 +4276,16 @@
         <v>10</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="O59" s="7" t="n">
-        <v>45983.3518402778</v>
+        <v>45646.6471527778</v>
       </c>
       <c r="P59" s="6"/>
       <c r="Q59" s="7"/>
-      <c r="R59" s="6"/>
+      <c r="R59" s="6" t="s">
+        <v>198</v>
+      </c>
       <c r="S59" s="6" t="s">
         <v>28</v>
       </c>
@@ -4264,55 +4294,53 @@
       <c r="V59" s="6"/>
       <c r="W59" s="6"/>
     </row>
-    <row r="60" customHeight="1" ht="58">
+    <row r="60" customHeight="1" ht="20">
       <c r="A60" s="5" t="n">
-        <v>161</v>
+        <v>801</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>120</v>
+        <v>1200</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L60" s="5" t="n">
         <v>110</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="O60" s="7" t="n">
-        <v>44807.6812268519</v>
+        <v>45981.747025463</v>
       </c>
       <c r="P60" s="6"/>
       <c r="Q60" s="7"/>
-      <c r="R60" s="6" t="s">
-        <v>199</v>
-      </c>
+      <c r="R60" s="6"/>
       <c r="S60" s="6" t="s">
         <v>28</v>
       </c>
@@ -4323,35 +4351,35 @@
     </row>
     <row r="61" customHeight="1" ht="20">
       <c r="A61" s="5" t="n">
-        <v>361</v>
+        <v>822</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I61" s="6"/>
       <c r="J61" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L61" s="5" t="n">
         <v>110</v>
@@ -4360,16 +4388,16 @@
         <v>10</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="O61" s="7" t="n">
-        <v>45069</v>
+        <v>45983</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="Q61" s="7" t="n">
-        <v>45069.5181018519</v>
+        <v>46053.8096180556</v>
       </c>
       <c r="R61" s="6"/>
       <c r="S61" s="6" t="s">
@@ -4380,54 +4408,54 @@
       <c r="V61" s="6"/>
       <c r="W61" s="6"/>
     </row>
-    <row r="62" customHeight="1" ht="20">
+    <row r="62" customHeight="1" ht="58">
       <c r="A62" s="5" t="n">
-        <v>681</v>
+        <v>161</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>49</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>1200</v>
+        <v>120</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L62" s="5" t="n">
         <v>110</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="O62" s="7" t="n">
-        <v>45793.6175462963</v>
+        <v>44807.6812268519</v>
       </c>
       <c r="P62" s="6"/>
       <c r="Q62" s="7"/>
       <c r="R62" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="S62" s="6" t="s">
         <v>28</v>
@@ -4439,35 +4467,35 @@
     </row>
     <row r="63" customHeight="1" ht="20">
       <c r="A63" s="5" t="n">
-        <v>722</v>
+        <v>361</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F63" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1100</v>
+        <v>550</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I63" s="6"/>
       <c r="J63" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L63" s="5" t="n">
         <v>110</v>
@@ -4476,13 +4504,17 @@
         <v>10</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>45908.4576388889</v>
-      </c>
-      <c r="P63" s="6"/>
-      <c r="Q63" s="7"/>
+        <v>45069</v>
+      </c>
+      <c r="P63" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q63" s="7" t="n">
+        <v>45069.5181018519</v>
+      </c>
       <c r="R63" s="6"/>
       <c r="S63" s="6" t="s">
         <v>28</v>
@@ -4491,6 +4523,118 @@
       <c r="U63" s="6"/>
       <c r="V63" s="6"/>
       <c r="W63" s="6"/>
+    </row>
+    <row r="64" customHeight="1" ht="20">
+      <c r="A64" s="5" t="n">
+        <v>681</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I64" s="6"/>
+      <c r="J64" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="O64" s="7" t="n">
+        <v>45793.6175462963</v>
+      </c>
+      <c r="P64" s="6"/>
+      <c r="Q64" s="7"/>
+      <c r="R64" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="S64" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="T64" s="6"/>
+      <c r="U64" s="6"/>
+      <c r="V64" s="6"/>
+      <c r="W64" s="6"/>
+    </row>
+    <row r="65" customHeight="1" ht="20">
+      <c r="A65" s="5" t="n">
+        <v>722</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I65" s="6"/>
+      <c r="J65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="M65" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N65" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="O65" s="7" t="n">
+        <v>45908.4576388889</v>
+      </c>
+      <c r="P65" s="6"/>
+      <c r="Q65" s="7"/>
+      <c r="R65" s="6"/>
+      <c r="S65" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="T65" s="6"/>
+      <c r="U65" s="6"/>
+      <c r="V65" s="6"/>
+      <c r="W65" s="6"/>
     </row>
   </sheetData>
   <tableParts count="1">
